--- a/docs/assets/Cafeteria-Aurora-Modelo-Financiero.xlsx
+++ b/docs/assets/Cafeteria-Aurora-Modelo-Financiero.xlsx
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="B53" s="39">
-        <f>"Personal 2027: "&amp;TEXT(Base!C79,"#,##0 €")&amp;" · ingresos por FTE: "&amp;TEXT(Base!C76/Base!C9,"#,##0 €")</f>
+        <f>"Personal 2027: "&amp;TEXT(Base!C79,"#,##0 €")&amp;" · ingresos por FTE: "&amp;TEXT(Base!C76/Personal!D9,"#,##0 €")</f>
         <v/>
       </c>
     </row>

--- a/docs/assets/Cafeteria-Aurora-Modelo-Financiero.xlsx
+++ b/docs/assets/Cafeteria-Aurora-Modelo-Financiero.xlsx
@@ -909,9 +909,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Resumen'!$A$151:$A$153</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -936,9 +936,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Resumen'!$A$151:$A$153</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -963,9 +963,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Resumen'!$A$151:$A$153</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1066,9 +1066,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Resumen'!$B$158:$B$165</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1162,9 +1162,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Resumen'!$B$169:$B$173</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
